--- a/data/выпуск_продукции.xlsx
+++ b/data/выпуск_продукции.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s.kulikova\Desktop\ИИ\Аналитика данных по качеству\АН\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Отделы\Дирекция по организационному развитию и системе менеджмента качества\ОРСМК\Несоответствия\Инструкции и классификаторы\МОЕ\ИИ\Аналитика данных по качеству\АН\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03440A50-DD52-497A-A6F0-97E795EAF245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D442AB-E6B1-42D6-91B0-54631115CC7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2895" yWindow="-15060" windowWidth="16590" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2985" yWindow="-14100" windowWidth="16590" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Выпуск" sheetId="1" r:id="rId1"/>
@@ -550,9 +550,15 @@
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="B8" s="3">
+        <v>3040</v>
+      </c>
+      <c r="C8" s="3">
+        <v>3315</v>
+      </c>
+      <c r="D8" s="3">
+        <v>43.51</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
